--- a/per-stock/HTHIY/financials.xlsx
+++ b/per-stock/HTHIY/financials.xlsx
@@ -1,19 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income stmt (annual)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income stmt (quarterly)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance sheet (annual)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash flow (annual)" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash flow (quarterly)" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data flags" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="FY Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Income stmt (annual)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Income stmt (quarterly)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Balance sheet (annual)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Balance sheet (quarterly)" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Cash flow (annual)" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Cash flow (quarterly)" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Data flags" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +24,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.00&quot;x&quot;"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -61,11 +67,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -531,7 +540,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>137062752256</v>
+        <v>135398473728</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -546,7 +555,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-327377616896</v>
+        <v>-328830222336</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -561,7 +570,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>27.196428</v>
+        <v>27.372726</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -576,7 +585,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>12.282258</v>
+        <v>12.1411295</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -591,7 +600,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.012946594</v>
+        <v>0.01278939</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -715,7 +724,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>yfinance info.freeCashflow</t>
+          <t>yfinance info.freeCashflow (FALLBACK levered estimate — statement TTM unavailable)</t>
         </is>
       </c>
     </row>
@@ -726,7 +735,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4499762162</v>
+        <v>4496794318</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -741,7 +750,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>30.46</v>
+        <v>30.11</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -785,6 +794,459 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Fiscal-year summary (GAAP, $ except where noted)</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>FY-3</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>FY-2</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>FY-1</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>TTM</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Source / formula</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Fiscal period end</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2023-03-31</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2024-03-31</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>TTM → 2025-12-31</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>annual statement headers; TTM = Σ last 4 quarters</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B3" s="3">
+        <f>'Income stmt (annual)'!D41</f>
+        <v/>
+      </c>
+      <c r="C3" s="3">
+        <f>'Income stmt (annual)'!C41</f>
+        <v/>
+      </c>
+      <c r="D3" s="3">
+        <f>'Income stmt (annual)'!B41</f>
+        <v/>
+      </c>
+      <c r="E3" s="3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="B4" s="3">
+        <f>'Income stmt (annual)'!D39</f>
+        <v/>
+      </c>
+      <c r="C4" s="3">
+        <f>'Income stmt (annual)'!C39</f>
+        <v/>
+      </c>
+      <c r="D4" s="3">
+        <f>'Income stmt (annual)'!B39</f>
+        <v/>
+      </c>
+      <c r="E4" s="3" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gross Profit (GAAP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="B5" s="4">
+        <f>IFERROR(B4/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C5" s="4">
+        <f>IFERROR(C4/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D5" s="4">
+        <f>IFERROR(D4/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E5" s="4">
+        <f>IFERROR(E4/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>GAAP = gross profit / revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Operating income</t>
+        </is>
+      </c>
+      <c r="B6" s="3">
+        <f>'Income stmt (annual)'!D35</f>
+        <v/>
+      </c>
+      <c r="C6" s="3">
+        <f>'Income stmt (annual)'!C35</f>
+        <v/>
+      </c>
+      <c r="D6" s="3">
+        <f>'Income stmt (annual)'!B35</f>
+        <v/>
+      </c>
+      <c r="E6" s="3" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Operating Income</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Operating margin %</t>
+        </is>
+      </c>
+      <c r="B7" s="4">
+        <f>IFERROR(B6/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C7" s="4">
+        <f>IFERROR(C6/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D7" s="4">
+        <f>IFERROR(D6/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E7" s="4">
+        <f>IFERROR(E6/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F7">
+        <f> operating income / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B8" s="3">
+        <f>'Income stmt (annual)'!D8</f>
+        <v/>
+      </c>
+      <c r="C8" s="3">
+        <f>'Income stmt (annual)'!C8</f>
+        <v/>
+      </c>
+      <c r="D8" s="3">
+        <f>'Income stmt (annual)'!B8</f>
+        <v/>
+      </c>
+      <c r="E8" s="3" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Free cash flow</t>
+        </is>
+      </c>
+      <c r="B9" s="3">
+        <f>'Cash flow (annual)'!D2</f>
+        <v/>
+      </c>
+      <c r="C9" s="3">
+        <f>'Cash flow (annual)'!C2</f>
+        <v/>
+      </c>
+      <c r="D9" s="3">
+        <f>'Cash flow (annual)'!B2</f>
+        <v/>
+      </c>
+      <c r="E9" s="3" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>FCF = OCF − capex</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>FCF margin %</t>
+        </is>
+      </c>
+      <c r="B10" s="4">
+        <f>IFERROR(B9/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C10" s="4">
+        <f>IFERROR(C9/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D10" s="4">
+        <f>IFERROR(D9/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E10" s="4">
+        <f>IFERROR(E9/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F10">
+        <f> FCF / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Capex</t>
+        </is>
+      </c>
+      <c r="B11" s="3">
+        <f>-'Cash flow (annual)'!D7</f>
+        <v/>
+      </c>
+      <c r="C11" s="3">
+        <f>-'Cash flow (annual)'!C7</f>
+        <v/>
+      </c>
+      <c r="D11" s="3">
+        <f>-'Cash flow (annual)'!B7</f>
+        <v/>
+      </c>
+      <c r="E11" s="3" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Capex (shown positive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Capex / revenue %</t>
+        </is>
+      </c>
+      <c r="B12" s="4">
+        <f>IFERROR(B11/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C12" s="4">
+        <f>IFERROR(C11/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D12" s="4">
+        <f>IFERROR(D11/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E12" s="4">
+        <f>IFERROR(E11/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F12">
+        <f> capex / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Net debt</t>
+        </is>
+      </c>
+      <c r="B13" s="3">
+        <f>'Balance sheet (annual)'!D5</f>
+        <v/>
+      </c>
+      <c r="C13" s="3">
+        <f>'Balance sheet (annual)'!C5</f>
+        <v/>
+      </c>
+      <c r="D13" s="3">
+        <f>'Balance sheet (annual)'!B5</f>
+        <v/>
+      </c>
+      <c r="E13" s="3">
+        <f>'Balance sheet (quarterly)'!B5</f>
+        <v/>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Net debt; TTM = MRQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Net debt / EBITDA</t>
+        </is>
+      </c>
+      <c r="B14" s="5">
+        <f>IFERROR(B13/B8,"")</f>
+        <v/>
+      </c>
+      <c r="C14" s="5">
+        <f>IFERROR(C13/C8,"")</f>
+        <v/>
+      </c>
+      <c r="D14" s="5">
+        <f>IFERROR(D13/D8,"")</f>
+        <v/>
+      </c>
+      <c r="E14" s="5">
+        <f>IFERROR(E13/E8,"")</f>
+        <v/>
+      </c>
+      <c r="F14">
+        <f> net debt / EBITDA</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Share count (period-end, M)</t>
+        </is>
+      </c>
+      <c r="B15" s="6">
+        <f>'Balance sheet (annual)'!D3/1e6</f>
+        <v/>
+      </c>
+      <c r="C15" s="6">
+        <f>'Balance sheet (annual)'!C3/1e6</f>
+        <v/>
+      </c>
+      <c r="D15" s="6">
+        <f>'Balance sheet (annual)'!B3/1e6</f>
+        <v/>
+      </c>
+      <c r="E15" s="6">
+        <f>'Balance sheet (quarterly)'!B3/1e6</f>
+        <v/>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>shares ÷ 1e6; TTM = MRQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Share count YoY %</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr"/>
+      <c r="C16" s="4">
+        <f>IFERROR(C15/B15-1,"")</f>
+        <v/>
+      </c>
+      <c r="D16" s="4">
+        <f>IFERROR(D15/C15-1,"")</f>
+        <v/>
+      </c>
+      <c r="E16" s="4">
+        <f>IFERROR(E15/D15-1,"")</f>
+        <v/>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>vs prior period</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1605,7 +2067,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1689,7 +2151,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2666,7 +3128,825 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D50"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>2025-03-31</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>2024-09-30</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Treasury Shares Number</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>44295189</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>2467109</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>39170258</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Ordinary Shares Number</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>4537265796</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>4577874576</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>4597399127</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Share Issued</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>4581560985</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>4580341685</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>4636569385</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Net Debt</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n"/>
+      <c r="C5" s="3" t="n">
+        <v>339874000000</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>734820000000</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Total Debt</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>1208444000000</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>1206116000000</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>1529084000000</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Tangible Book Value</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>2427233000000</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>2160272000000</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>1887649000000</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Invested Capital</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>7328150000000</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>7053207000000</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>7030444000000</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Working Capital</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>990790000000</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>689998000000</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>823151000000</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Net Tangible Assets</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>2427233000000</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>2160272000000</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>1887649000000</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Common Stock Equity</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>6119706000000</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>5847091000000</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>5501360000000</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Total Capitalization</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>6956556000000</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>6611243000000</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>6466586000000</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Total Equity Gross Minority Interest</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>6291665000000</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>6031417000000</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>5655599000000</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Minority Interest</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>171959000000</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>184326000000</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>154239000000</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Stockholders Equity</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>6119706000000</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>5847091000000</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>5501360000000</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Treasury Stock</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>179359000000</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>8587000000</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>127659000000</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Retained Earnings</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>4724327000000</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>4350503000000</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>4282935000000</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Additional Paid In Capital</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>5206000000</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" s="3" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Capital Stock</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>466666000000</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>464384000000</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>464384000000</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Common Stock</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>466666000000</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>464384000000</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>464384000000</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Total Liabilities Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>7595478000000</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>7253396000000</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>6913029000000</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Total Non Current Liabilities Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>1411590000000</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>1345551000000</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>1587992000000</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Other Non Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>322048000000</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>333902000000</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>353998000000</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Non Current Pension And Other Postretirement Benefit Plans</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>252692000000</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>247497000000</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>268768000000</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Long Term Debt And Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>836850000000</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>764152000000</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>965226000000</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Long Term Debt</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>836850000000</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>764152000000</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>965226000000</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>6183888000000</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>5907845000000</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>5325037000000</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Other Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>739587000000</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>680411000000</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>573345000000</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Current Debt And Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>371594000000</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>441964000000</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>563858000000</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Current Debt</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>371594000000</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>441964000000</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>563858000000</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Payables</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>1587573000000</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>1572764000000</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>1462387000000</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Accounts Payable</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>1587573000000</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>1572764000000</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>1462387000000</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Total Assets</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>13887143000000</v>
+      </c>
+      <c r="C33" s="3" t="n">
+        <v>13284813000000</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v>12568628000000</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Total Non Current Assets</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>6712465000000</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>6686970000000</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>6420440000000</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Other Non Current Assets</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>482649000000</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>472816000000</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>456691000000</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Investmentin Financial Assets</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>369725000000</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>349567000000</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>332906000000</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Available For Sale Securities</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>369725000000</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>349567000000</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>332906000000</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Long Term Equity Investment</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>718026000000</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>836231000000</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>797376000000</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Goodwill And Other Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="n">
+        <v>3692473000000</v>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>3686819000000</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>3613711000000</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Other Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v>1188462000000</v>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>1199996000000</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>1219378000000</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Goodwill</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v>2504011000000</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>2486823000000</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>2394333000000</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Net PPE</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>1449592000000</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>1341537000000</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>1219756000000</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Current Assets</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>7174678000000</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>6597843000000</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>6148188000000</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Other Current Assets</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>431392000000</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>350558000000</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>361470000000</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Inventory</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="n">
+        <v>1762698000000</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>1566282000000</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>1606906000000</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v>3373227000000</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>3496340000000</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>3080101000000</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="n"/>
+      <c r="C47" s="3" t="n"/>
+      <c r="D47" s="3" t="n">
+        <v>3080101000000</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Cash Cash Equivalents And Short Term Investments</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v>1607361000000</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>1184663000000</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>1099711000000</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Other Short Term Investments</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="n">
+        <v>328426000000</v>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>318421000000</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>305447000000</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Cash And Cash Equivalents</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v>1278935000000</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>866242000000</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>794264000000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3626,7 +4906,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3647,7 +4927,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3675,12 +4955,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>FY Summary</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>no gaps detected</t>
+          <t>TTM uses only 2 quarters (&lt;4 available)</t>
         </is>
       </c>
     </row>
